--- a/Exercices/Block 1 - Forecasting/1_Forecasting_Correction - Anotated Raph.xlsx
+++ b/Exercices/Block 1 - Forecasting/1_Forecasting_Correction - Anotated Raph.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universitelibrebruxelles-my.sharepoint.com/personal/raphael_humblet_ulb_be/Documents/ULB/MA2/ULB-GEST-H501/Exercices/Block 1 - Forecasting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="183" documentId="13_ncr:1_{3F8A16A5-5458-2B4A-A85F-5EA095FD1B31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B1A68F3-1E5C-478A-8A75-6C800147FD87}"/>
+  <xr:revisionPtr revIDLastSave="195" documentId="13_ncr:1_{3F8A16A5-5458-2B4A-A85F-5EA095FD1B31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3B93659-B867-4944-8A91-DDC5BDC261D1}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="15" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Naïve" sheetId="16" r:id="rId1"/>
@@ -850,7 +850,7 @@
     <numFmt numFmtId="170" formatCode="#,##0.000"/>
     <numFmt numFmtId="171" formatCode="0.0"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1008,7 +1008,12 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1375,7 +1380,7 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="179">
+  <cellXfs count="181">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1683,7 +1688,6 @@
     <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="15" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1759,14 +1763,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="6">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="5" builtinId="4"/>
+    <cellStyle name="Milliers" xfId="1" builtinId="3"/>
+    <cellStyle name="Monétaire" xfId="5" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="3" xr:uid="{3858FDAA-B3E1-5C4F-85A9-0CA787CDDBCF}"/>
-    <cellStyle name="Per cent" xfId="2" builtinId="5"/>
     <cellStyle name="Per cent 2" xfId="4" xr:uid="{F01528EF-3DA0-DF43-B078-CFA947FA6E1C}"/>
+    <cellStyle name="Pourcentage" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1784,7 +1793,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2477,7 +2486,7 @@
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3156,7 +3165,7 @@
 <file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3554,7 +3563,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4224,7 +4233,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4894,7 +4903,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5380,7 +5389,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5863,7 +5872,7 @@
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6340,7 +6349,7 @@
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6877,7 +6886,7 @@
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7423,7 +7432,7 @@
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -14624,6 +14633,50 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>26928</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>153933</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>114975</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Image 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71F972BD-5D3C-0715-C699-2BF701A34E4A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="660341" y="3552825"/>
+          <a:ext cx="3294067" cy="1448475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -15546,6 +15599,50 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>510267</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>89331</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>209152</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>138285</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Image 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{778B443A-F3F9-1456-7C9E-F6E8A7F42E40}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4483553" y="3579564"/>
+          <a:ext cx="2862546" cy="1518525"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -16384,8 +16481,12 @@
 </externalLink>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -16682,9 +16783,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{712437DE-CE02-4F49-942E-CEDCE6CF2B1E}">
   <dimension ref="A1:Q28"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
@@ -16695,7 +16796,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="15">
         <v>1</v>
       </c>
@@ -16704,7 +16805,7 @@
       </c>
       <c r="C2" s="53"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="15">
         <v>2</v>
       </c>
@@ -16716,7 +16817,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="15">
         <v>3</v>
       </c>
@@ -16728,7 +16829,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="15">
         <v>4</v>
       </c>
@@ -16740,7 +16841,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" s="15">
         <v>5</v>
       </c>
@@ -16752,7 +16853,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" s="15">
         <v>6</v>
       </c>
@@ -16764,7 +16865,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" s="15">
         <v>7</v>
       </c>
@@ -16776,7 +16877,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" s="15">
         <v>8</v>
       </c>
@@ -16788,7 +16889,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" s="15">
         <v>9</v>
       </c>
@@ -16800,7 +16901,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" s="15">
         <v>10</v>
       </c>
@@ -16812,7 +16913,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" s="15">
         <v>11</v>
       </c>
@@ -16822,7 +16923,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" s="15">
         <v>12</v>
       </c>
@@ -16832,7 +16933,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" s="15">
         <v>13</v>
       </c>
@@ -16842,52 +16943,52 @@
         <v>232</v>
       </c>
     </row>
-    <row r="19" spans="17:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="17:17" x14ac:dyDescent="0.45">
       <c r="Q19">
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="17:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="17:17" x14ac:dyDescent="0.45">
       <c r="Q20">
         <v>49</v>
       </c>
     </row>
-    <row r="21" spans="17:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="17:17" x14ac:dyDescent="0.45">
       <c r="Q21">
         <v>46</v>
       </c>
     </row>
-    <row r="22" spans="17:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="17:17" x14ac:dyDescent="0.45">
       <c r="Q22">
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="17:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="17:17" x14ac:dyDescent="0.45">
       <c r="Q23">
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="17:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="17:17" x14ac:dyDescent="0.45">
       <c r="Q24">
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="17:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="17:17" x14ac:dyDescent="0.45">
       <c r="Q25">
         <v>43</v>
       </c>
     </row>
-    <row r="26" spans="17:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="17:17" x14ac:dyDescent="0.45">
       <c r="Q26">
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="17:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="17:17" x14ac:dyDescent="0.45">
       <c r="Q27">
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="17:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="17:17" x14ac:dyDescent="0.45">
       <c r="Q28">
         <v>40</v>
       </c>
@@ -16901,21 +17002,21 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAEB56E2-6BF5-415B-96ED-BAEA54D3B700}">
   <dimension ref="A1:S25"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" customWidth="1"/>
-    <col min="2" max="5" width="23.42578125" customWidth="1"/>
-    <col min="12" max="12" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.3984375" customWidth="1"/>
+    <col min="2" max="5" width="23.3984375" customWidth="1"/>
+    <col min="12" max="12" width="9.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="163" t="s">
+    <row r="1" spans="1:16" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="162" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="163" t="s">
+      <c r="B1" s="162" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="163" t="s">
+      <c r="C1" s="162" t="s">
         <v>38</v>
       </c>
       <c r="D1" s="49" t="s">
@@ -16924,17 +17025,17 @@
       <c r="E1" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="173" t="s">
+      <c r="F1" s="172" t="s">
         <v>126</v>
       </c>
-      <c r="G1" s="173" t="s">
+      <c r="G1" s="172" t="s">
         <v>127</v>
       </c>
-      <c r="H1" s="173" t="s">
+      <c r="H1" s="172" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A2" s="25">
         <v>1</v>
       </c>
@@ -16956,7 +17057,7 @@
         <f>AVERAGE(B2:B9)</f>
         <v>3.5</v>
       </c>
-      <c r="G2" s="174">
+      <c r="G2" s="173">
         <f>AVERAGE(C2:C9)</f>
         <v>3.2749999999999999</v>
       </c>
@@ -16965,7 +17066,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A3" s="25">
         <v>2</v>
       </c>
@@ -16984,7 +17085,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A4" s="25">
         <v>3</v>
       </c>
@@ -17006,7 +17107,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="25">
         <v>4</v>
       </c>
@@ -17025,7 +17126,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A6" s="25">
         <v>5</v>
       </c>
@@ -17043,12 +17144,12 @@
         <f t="shared" si="1"/>
         <v>14.8</v>
       </c>
-      <c r="K6" s="159" t="s">
+      <c r="K6" s="158" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="159"/>
-    </row>
-    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="L6" s="158"/>
+    </row>
+    <row r="7" spans="1:16" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A7" s="25">
         <v>6</v>
       </c>
@@ -17073,7 +17174,7 @@
         <v>0.99443480052579969</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A8" s="25">
         <v>7</v>
       </c>
@@ -17098,7 +17199,7 @@
         <v>0.98890057249678698</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A9" s="25">
         <v>8</v>
       </c>
@@ -17123,7 +17224,7 @@
         <v>0.98705066791291818</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A10" s="40" t="s">
         <v>46</v>
       </c>
@@ -17146,7 +17247,7 @@
         <v>9.3788572311856361E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A11" s="20"/>
       <c r="B11" s="45" t="s">
         <v>49</v>
@@ -17162,14 +17263,14 @@
         <f>SUM(E2:E10)</f>
         <v>100.9</v>
       </c>
-      <c r="K11" s="157" t="s">
+      <c r="K11" s="156" t="s">
         <v>51</v>
       </c>
-      <c r="L11" s="157">
+      <c r="L11" s="156">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B13" s="34" t="s">
         <v>52</v>
       </c>
@@ -17188,8 +17289,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="164" t="s">
+    <row r="14" spans="1:16" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="B14" s="163" t="s">
         <v>54</v>
       </c>
       <c r="C14" s="39">
@@ -17198,24 +17299,24 @@
       </c>
       <c r="D14" s="20"/>
       <c r="E14" s="20"/>
-      <c r="K14" s="158"/>
-      <c r="L14" s="158" t="s">
+      <c r="K14" s="157"/>
+      <c r="L14" s="157" t="s">
         <v>55</v>
       </c>
-      <c r="M14" s="158" t="s">
+      <c r="M14" s="157" t="s">
         <v>56</v>
       </c>
-      <c r="N14" s="158" t="s">
+      <c r="N14" s="157" t="s">
         <v>57</v>
       </c>
-      <c r="O14" s="158" t="s">
+      <c r="O14" s="157" t="s">
         <v>58</v>
       </c>
-      <c r="P14" s="158" t="s">
+      <c r="P14" s="157" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.45">
       <c r="K15" t="s">
         <v>60</v>
       </c>
@@ -17235,7 +17336,7 @@
         <v>4.2910912101752315E-7</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" ht="33.75" x14ac:dyDescent="0.5">
       <c r="A16" s="36" t="s">
         <v>61</v>
       </c>
@@ -17256,7 +17357,7 @@
         <v>8.7962962962963107E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A17" s="23" t="s">
         <v>63</v>
       </c>
@@ -17270,20 +17371,20 @@
         <v>66</v>
       </c>
       <c r="E17" s="20"/>
-      <c r="K17" s="157" t="s">
+      <c r="K17" s="156" t="s">
         <v>67</v>
       </c>
-      <c r="L17" s="157">
+      <c r="L17" s="156">
         <v>7</v>
       </c>
-      <c r="M17" s="157">
+      <c r="M17" s="156">
         <v>4.7550000000000008</v>
       </c>
-      <c r="N17" s="157"/>
-      <c r="O17" s="157"/>
-      <c r="P17" s="157"/>
-    </row>
-    <row r="18" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N17" s="156"/>
+      <c r="O17" s="156"/>
+      <c r="P17" s="156"/>
+    </row>
+    <row r="18" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A18" s="25">
         <v>3</v>
       </c>
@@ -17298,41 +17399,41 @@
       </c>
       <c r="E18" s="35"/>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="K19" s="158"/>
-      <c r="L19" s="158" t="s">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="K19" s="157"/>
+      <c r="L19" s="157" t="s">
         <v>68</v>
       </c>
-      <c r="M19" s="158" t="s">
+      <c r="M19" s="157" t="s">
         <v>48</v>
       </c>
-      <c r="N19" s="158" t="s">
+      <c r="N19" s="157" t="s">
         <v>69</v>
       </c>
-      <c r="O19" s="158" t="s">
+      <c r="O19" s="157" t="s">
         <v>70</v>
       </c>
-      <c r="P19" s="158" t="s">
+      <c r="P19" s="157" t="s">
         <v>71</v>
       </c>
-      <c r="Q19" s="158" t="s">
+      <c r="Q19" s="157" t="s">
         <v>72</v>
       </c>
-      <c r="R19" s="158" t="s">
+      <c r="R19" s="157" t="s">
         <v>73</v>
       </c>
-      <c r="S19" s="158" t="s">
+      <c r="S19" s="157" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" ht="16.899999999999999" x14ac:dyDescent="0.45">
       <c r="A20" s="37" t="s">
         <v>2</v>
       </c>
       <c r="K20" t="s">
         <v>75</v>
       </c>
-      <c r="L20" s="160">
+      <c r="L20" s="159">
         <v>1.4861111111111101</v>
       </c>
       <c r="M20">
@@ -17357,7 +17458,7 @@
         <v>1.6920868160343343</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A21" s="33" t="s">
         <v>76</v>
       </c>
@@ -17367,35 +17468,35 @@
       <c r="J21" t="s">
         <v>77</v>
       </c>
-      <c r="K21" s="157" t="s">
+      <c r="K21" s="156" t="s">
         <v>78</v>
       </c>
-      <c r="L21" s="161">
+      <c r="L21" s="160">
         <v>0.51111111111111129</v>
       </c>
-      <c r="M21" s="157">
+      <c r="M21" s="156">
         <v>2.210617849317284E-2</v>
       </c>
-      <c r="N21" s="157">
+      <c r="N21" s="156">
         <v>23.120735737701576</v>
       </c>
-      <c r="O21" s="157">
+      <c r="O21" s="156">
         <v>4.2910912101752315E-7</v>
       </c>
-      <c r="P21" s="157">
+      <c r="P21" s="156">
         <v>0.45701924097264063</v>
       </c>
-      <c r="Q21" s="157">
+      <c r="Q21" s="156">
         <v>0.56520298124958201</v>
       </c>
-      <c r="R21" s="157">
+      <c r="R21" s="156">
         <v>0.45701924097264063</v>
       </c>
-      <c r="S21" s="157">
+      <c r="S21" s="156">
         <v>0.56520298124958201</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A22" s="32" t="s">
         <v>79</v>
       </c>
@@ -17404,7 +17505,7 @@
         <v>3.0194444444444444</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A23" s="32" t="s">
         <v>64</v>
       </c>
@@ -17413,7 +17514,7 @@
         <v>3.5305555555555554</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A24" s="32" t="s">
         <v>65</v>
       </c>
@@ -17422,7 +17523,7 @@
         <v>4.0416666666666661</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A25" s="32" t="s">
         <v>65</v>
       </c>
@@ -17440,17 +17541,17 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DD0916E-BEC1-45D1-A1C4-8C53C548CF15}">
   <dimension ref="A1:I31"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" customWidth="1"/>
-    <col min="3" max="3" width="28.140625" customWidth="1"/>
-    <col min="4" max="4" width="22.28515625" customWidth="1"/>
+    <col min="1" max="1" width="17.3984375" customWidth="1"/>
+    <col min="2" max="2" width="19.3984375" customWidth="1"/>
+    <col min="3" max="3" width="28.1328125" customWidth="1"/>
+    <col min="4" max="4" width="22.265625" customWidth="1"/>
     <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="17.140625" customWidth="1"/>
+    <col min="7" max="9" width="17.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="77" t="s">
         <v>36</v>
       </c>
@@ -17470,7 +17571,7 @@
       <c r="H1" s="19"/>
       <c r="I1" s="19"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="15" x14ac:dyDescent="0.45">
       <c r="A2" s="25">
         <v>1</v>
       </c>
@@ -17490,7 +17591,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="15" x14ac:dyDescent="0.45">
       <c r="A3" s="25">
         <v>2</v>
       </c>
@@ -17516,7 +17617,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="15" x14ac:dyDescent="0.45">
       <c r="A4" s="25">
         <v>3</v>
       </c>
@@ -17542,7 +17643,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="15" x14ac:dyDescent="0.45">
       <c r="A5" s="25">
         <v>4</v>
       </c>
@@ -17562,7 +17663,7 @@
       <c r="H5" s="20"/>
       <c r="I5" s="20"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="15" x14ac:dyDescent="0.45">
       <c r="A6" s="25">
         <v>5</v>
       </c>
@@ -17588,7 +17689,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="15" x14ac:dyDescent="0.45">
       <c r="A7" s="25">
         <v>6</v>
       </c>
@@ -17614,7 +17715,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="15" x14ac:dyDescent="0.45">
       <c r="A8" s="25">
         <v>7</v>
       </c>
@@ -17632,7 +17733,7 @@
       <c r="H8" s="75"/>
       <c r="I8" s="75"/>
     </row>
-    <row r="9" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="16.899999999999999" x14ac:dyDescent="0.45">
       <c r="A9" s="25">
         <v>8</v>
       </c>
@@ -17647,7 +17748,7 @@
       </c>
       <c r="F9" s="22"/>
     </row>
-    <row r="10" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="23" t="s">
         <v>86</v>
       </c>
@@ -17664,7 +17765,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="15" x14ac:dyDescent="0.45">
       <c r="F11" s="23" t="s">
         <v>76</v>
       </c>
@@ -17672,7 +17773,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="15" x14ac:dyDescent="0.45">
       <c r="F12" s="25" t="s">
         <v>79</v>
       </c>
@@ -17681,7 +17782,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="15" x14ac:dyDescent="0.45">
       <c r="F13" s="25" t="s">
         <v>64</v>
       </c>
@@ -17690,7 +17791,7 @@
         <v>3.9311111111111119</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="15" x14ac:dyDescent="0.45">
       <c r="F14" s="25" t="s">
         <v>65</v>
       </c>
@@ -17699,7 +17800,7 @@
         <v>3.5911111111111111</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="15" x14ac:dyDescent="0.45">
       <c r="F15" s="25" t="s">
         <v>66</v>
       </c>
@@ -17708,13 +17809,13 @@
         <v>3.1833333333333336</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A28" s="79"/>
       <c r="B28" s="79" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A29" s="80" t="s">
         <v>88</v>
       </c>
@@ -17722,7 +17823,7 @@
         <v>3.1444444444444453</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A30" s="80" t="s">
         <v>84</v>
       </c>
@@ -17730,7 +17831,7 @@
         <v>-0.33333333333333343</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A31" s="80" t="s">
         <v>85</v>
       </c>
@@ -17746,12 +17847,12 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50A6771D-FFCC-431B-8E39-936F7DC5ACF2}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="8" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="33" x14ac:dyDescent="0.45">
       <c r="A1" s="58" t="s">
         <v>89</v>
       </c>
@@ -17777,7 +17878,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="15" x14ac:dyDescent="0.45">
       <c r="A2" s="25">
         <v>1</v>
       </c>
@@ -17793,7 +17894,7 @@
       <c r="G2" s="28"/>
       <c r="H2" s="62"/>
     </row>
-    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="15" x14ac:dyDescent="0.45">
       <c r="A3" s="25">
         <v>2</v>
       </c>
@@ -17809,7 +17910,7 @@
       <c r="G3" s="28"/>
       <c r="H3" s="62"/>
     </row>
-    <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="15" x14ac:dyDescent="0.45">
       <c r="A4" s="25">
         <v>3</v>
       </c>
@@ -17825,7 +17926,7 @@
       <c r="G4" s="28"/>
       <c r="H4" s="62"/>
     </row>
-    <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="15" x14ac:dyDescent="0.45">
       <c r="A5" s="25">
         <v>4</v>
       </c>
@@ -17841,7 +17942,7 @@
       <c r="G5" s="28"/>
       <c r="H5" s="62"/>
     </row>
-    <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="15" x14ac:dyDescent="0.45">
       <c r="A6" s="25">
         <v>5</v>
       </c>
@@ -17857,7 +17958,7 @@
       <c r="G6" s="28"/>
       <c r="H6" s="62"/>
     </row>
-    <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="15" x14ac:dyDescent="0.45">
       <c r="A7" s="25">
         <v>6</v>
       </c>
@@ -17881,12 +17982,12 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A4C187D-E52F-4CB3-A6B3-5029E5A03CB9}">
   <dimension ref="A3:F17"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="6" width="16.85546875" customWidth="1"/>
+    <col min="1" max="6" width="16.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="51.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="50.65" x14ac:dyDescent="0.5">
       <c r="A3" s="81" t="s">
         <v>89</v>
       </c>
@@ -17906,183 +18007,183 @@
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="165">
+    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A4" s="164">
         <v>1</v>
       </c>
-      <c r="B4" s="166">
+      <c r="B4" s="165">
         <v>300</v>
       </c>
-      <c r="C4" s="165">
+      <c r="C4" s="164">
         <v>299</v>
       </c>
-      <c r="D4" s="167"/>
-      <c r="E4" s="167"/>
-      <c r="F4" s="168"/>
-    </row>
-    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="165">
+      <c r="D4" s="166"/>
+      <c r="E4" s="166"/>
+      <c r="F4" s="167"/>
+    </row>
+    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A5" s="164">
         <v>2</v>
       </c>
-      <c r="B5" s="166">
+      <c r="B5" s="165">
         <v>300</v>
       </c>
-      <c r="C5" s="165">
+      <c r="C5" s="164">
         <v>305</v>
       </c>
-      <c r="D5" s="167"/>
-      <c r="E5" s="167"/>
-      <c r="F5" s="168"/>
-    </row>
-    <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="165">
+      <c r="D5" s="166"/>
+      <c r="E5" s="166"/>
+      <c r="F5" s="167"/>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A6" s="164">
         <v>3</v>
       </c>
-      <c r="B6" s="166">
+      <c r="B6" s="165">
         <v>300</v>
       </c>
-      <c r="C6" s="169">
+      <c r="C6" s="168">
         <v>312</v>
       </c>
-      <c r="D6" s="167"/>
-      <c r="E6" s="167"/>
-      <c r="F6" s="168"/>
-    </row>
-    <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="165">
+      <c r="D6" s="166"/>
+      <c r="E6" s="166"/>
+      <c r="F6" s="167"/>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A7" s="164">
         <v>4</v>
       </c>
-      <c r="B7" s="166">
+      <c r="B7" s="165">
         <v>300</v>
       </c>
-      <c r="C7" s="169">
+      <c r="C7" s="168">
         <v>310</v>
       </c>
-      <c r="D7" s="167"/>
-      <c r="E7" s="167"/>
-      <c r="F7" s="168"/>
-    </row>
-    <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="165">
+      <c r="D7" s="166"/>
+      <c r="E7" s="166"/>
+      <c r="F7" s="167"/>
+    </row>
+    <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A8" s="164">
         <v>5</v>
       </c>
-      <c r="B8" s="166">
+      <c r="B8" s="165">
         <v>300</v>
       </c>
-      <c r="C8" s="166">
+      <c r="C8" s="165">
         <v>294</v>
       </c>
-      <c r="D8" s="167"/>
-      <c r="E8" s="167"/>
-      <c r="F8" s="168"/>
-    </row>
-    <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="165">
+      <c r="D8" s="166"/>
+      <c r="E8" s="166"/>
+      <c r="F8" s="167"/>
+    </row>
+    <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A9" s="164">
         <v>6</v>
       </c>
-      <c r="B9" s="166">
+      <c r="B9" s="165">
         <v>300</v>
       </c>
-      <c r="C9" s="166">
+      <c r="C9" s="165">
         <v>315</v>
       </c>
-      <c r="D9" s="167"/>
-      <c r="E9" s="167"/>
-      <c r="F9" s="168"/>
-    </row>
-    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="165">
+      <c r="D9" s="166"/>
+      <c r="E9" s="166"/>
+      <c r="F9" s="167"/>
+    </row>
+    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A10" s="164">
         <v>7</v>
       </c>
-      <c r="B10" s="166">
+      <c r="B10" s="165">
         <v>300</v>
       </c>
-      <c r="C10" s="166">
+      <c r="C10" s="165">
         <v>306</v>
       </c>
-      <c r="D10" s="167"/>
-      <c r="E10" s="167"/>
-      <c r="F10" s="168"/>
-    </row>
-    <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="165">
+      <c r="D10" s="166"/>
+      <c r="E10" s="166"/>
+      <c r="F10" s="167"/>
+    </row>
+    <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A11" s="164">
         <v>8</v>
       </c>
-      <c r="B11" s="166">
+      <c r="B11" s="165">
         <v>300</v>
       </c>
-      <c r="C11" s="166">
+      <c r="C11" s="165">
         <v>286</v>
       </c>
-      <c r="D11" s="167"/>
-      <c r="E11" s="167"/>
-      <c r="F11" s="168"/>
-    </row>
-    <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="165">
+      <c r="D11" s="166"/>
+      <c r="E11" s="166"/>
+      <c r="F11" s="167"/>
+    </row>
+    <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A12" s="164">
         <v>9</v>
       </c>
-      <c r="B12" s="166">
+      <c r="B12" s="165">
         <v>300</v>
       </c>
-      <c r="C12" s="166">
+      <c r="C12" s="165">
         <v>292</v>
       </c>
-      <c r="D12" s="167"/>
-      <c r="E12" s="167"/>
-      <c r="F12" s="168"/>
-    </row>
-    <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="165">
+      <c r="D12" s="166"/>
+      <c r="E12" s="166"/>
+      <c r="F12" s="167"/>
+    </row>
+    <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A13" s="164">
         <v>10</v>
       </c>
-      <c r="B13" s="166">
+      <c r="B13" s="165">
         <v>300</v>
       </c>
-      <c r="C13" s="166">
+      <c r="C13" s="165">
         <v>285</v>
       </c>
-      <c r="D13" s="167"/>
-      <c r="E13" s="167"/>
-      <c r="F13" s="168"/>
-    </row>
-    <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="165">
+      <c r="D13" s="166"/>
+      <c r="E13" s="166"/>
+      <c r="F13" s="167"/>
+    </row>
+    <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A14" s="164">
         <v>11</v>
       </c>
-      <c r="B14" s="166">
+      <c r="B14" s="165">
         <v>300</v>
       </c>
-      <c r="C14" s="166">
+      <c r="C14" s="165">
         <v>311</v>
       </c>
-      <c r="D14" s="167"/>
-      <c r="E14" s="167"/>
-      <c r="F14" s="168"/>
-    </row>
-    <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="165">
+      <c r="D14" s="166"/>
+      <c r="E14" s="166"/>
+      <c r="F14" s="167"/>
+    </row>
+    <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A15" s="164">
         <v>12</v>
       </c>
-      <c r="B15" s="166">
+      <c r="B15" s="165">
         <v>300</v>
       </c>
-      <c r="C15" s="166">
+      <c r="C15" s="165">
         <v>285</v>
       </c>
-      <c r="D15" s="167"/>
-      <c r="E15" s="167"/>
-      <c r="F15" s="168"/>
-    </row>
-    <row r="16" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="D15" s="166"/>
+      <c r="E15" s="166"/>
+      <c r="F15" s="167"/>
+    </row>
+    <row r="16" spans="1:6" ht="16.899999999999999" x14ac:dyDescent="0.5">
       <c r="A16" s="84" t="s">
         <v>86</v>
       </c>
-      <c r="B16" s="170">
+      <c r="B16" s="169">
         <f>SUM(B4:B15)</f>
         <v>3600</v>
       </c>
-      <c r="C16" s="170">
+      <c r="C16" s="169">
         <f>SUM(C4:C15)</f>
         <v>3600</v>
       </c>
@@ -18090,16 +18191,16 @@
         <f>SUM(D4:D15)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="171">
+      <c r="E16" s="170">
         <f>SUM(E4:E15)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="172">
+      <c r="F16" s="171">
         <f>SUM(F4:F15)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="16.899999999999999" x14ac:dyDescent="0.5">
       <c r="A17" s="86"/>
       <c r="B17" s="87"/>
       <c r="C17" s="88"/>
@@ -18120,12 +18221,12 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{458CF3AA-F1A0-4831-9B70-6905CE41464F}">
   <dimension ref="A1:J13"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="10" width="15.140625" customWidth="1"/>
+    <col min="1" max="10" width="15.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="18" t="s">
         <v>89</v>
       </c>
@@ -18157,7 +18258,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="64">
         <v>1</v>
       </c>
@@ -18173,7 +18274,7 @@
       <c r="I2" s="64"/>
       <c r="J2" s="64"/>
     </row>
-    <row r="3" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="64">
         <v>2</v>
       </c>
@@ -18189,7 +18290,7 @@
       <c r="I3" s="64"/>
       <c r="J3" s="64"/>
     </row>
-    <row r="4" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="64">
         <v>3</v>
       </c>
@@ -18205,7 +18306,7 @@
       <c r="I4" s="64"/>
       <c r="J4" s="64"/>
     </row>
-    <row r="5" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="64">
         <v>4</v>
       </c>
@@ -18223,7 +18324,7 @@
       <c r="I5" s="67"/>
       <c r="J5" s="66"/>
     </row>
-    <row r="6" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="64">
         <v>5</v>
       </c>
@@ -18241,7 +18342,7 @@
       <c r="I6" s="67"/>
       <c r="J6" s="66"/>
     </row>
-    <row r="7" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="64">
         <v>6</v>
       </c>
@@ -18259,7 +18360,7 @@
       <c r="I7" s="67"/>
       <c r="J7" s="66"/>
     </row>
-    <row r="8" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="64">
         <v>7</v>
       </c>
@@ -18277,7 +18378,7 @@
       <c r="I8" s="67"/>
       <c r="J8" s="66"/>
     </row>
-    <row r="9" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="64">
         <v>8</v>
       </c>
@@ -18295,7 +18396,7 @@
       <c r="I9" s="67"/>
       <c r="J9" s="66"/>
     </row>
-    <row r="10" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="64">
         <v>9</v>
       </c>
@@ -18313,7 +18414,7 @@
       <c r="I10" s="67"/>
       <c r="J10" s="66"/>
     </row>
-    <row r="11" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="64">
         <v>10</v>
       </c>
@@ -18331,7 +18432,7 @@
       <c r="I11" s="67"/>
       <c r="J11" s="66"/>
     </row>
-    <row r="12" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="17" t="s">
         <v>102</v>
       </c>
@@ -18358,7 +18459,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="E13" s="16" t="s">
         <v>105</v>
       </c>
@@ -18375,17 +18476,17 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFD9A1A9-E779-2345-9BC3-1D90C45B4501}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.86328125" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" style="93" customWidth="1"/>
-    <col min="2" max="4" width="11.140625" style="93" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="93" customWidth="1"/>
-    <col min="6" max="11" width="11.140625" style="93" customWidth="1"/>
-    <col min="12" max="12" width="11.140625" style="92" hidden="1" customWidth="1"/>
-    <col min="13" max="16384" width="10.85546875" style="92"/>
+    <col min="1" max="1" width="11.73046875" style="93" customWidth="1"/>
+    <col min="2" max="4" width="11.1328125" style="93" customWidth="1"/>
+    <col min="5" max="5" width="14.3984375" style="93" customWidth="1"/>
+    <col min="6" max="11" width="11.1328125" style="93" customWidth="1"/>
+    <col min="12" max="12" width="11.1328125" style="92" hidden="1" customWidth="1"/>
+    <col min="13" max="16384" width="10.86328125" style="92"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="99" t="s">
         <v>89</v>
       </c>
@@ -18423,7 +18524,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" s="97">
         <v>1</v>
       </c>
@@ -18445,7 +18546,7 @@
         <f>D2^2</f>
         <v>1</v>
       </c>
-      <c r="G2" s="151">
+      <c r="G2" s="150">
         <f>E2/B2</f>
         <v>3.3444816053511705E-3</v>
       </c>
@@ -18470,7 +18571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A3" s="97">
         <v>2</v>
       </c>
@@ -18492,7 +18593,7 @@
         <f t="shared" ref="F3:F13" si="2">D3^2</f>
         <v>25</v>
       </c>
-      <c r="G3" s="151">
+      <c r="G3" s="150">
         <f t="shared" ref="G3:G13" si="3">E3/B3</f>
         <v>1.6393442622950821E-2</v>
       </c>
@@ -18517,7 +18618,7 @@
         <v>-1.3333333333333335</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A4" s="97">
         <v>3</v>
       </c>
@@ -18539,7 +18640,7 @@
         <f t="shared" si="2"/>
         <v>144</v>
       </c>
-      <c r="G4" s="151">
+      <c r="G4" s="150">
         <f t="shared" si="3"/>
         <v>3.8461538461538464E-2</v>
       </c>
@@ -18564,7 +18665,7 @@
         <v>-2.666666666666667</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A5" s="97">
         <v>4</v>
       </c>
@@ -18586,7 +18687,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="G5" s="151">
+      <c r="G5" s="150">
         <f t="shared" si="3"/>
         <v>3.2258064516129031E-2</v>
       </c>
@@ -18611,7 +18712,7 @@
         <v>-3.7142857142857144</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A6" s="97">
         <v>5</v>
       </c>
@@ -18633,7 +18734,7 @@
         <f t="shared" si="2"/>
         <v>36</v>
       </c>
-      <c r="G6" s="151">
+      <c r="G6" s="150">
         <f t="shared" si="3"/>
         <v>2.0408163265306121E-2</v>
       </c>
@@ -18658,7 +18759,7 @@
         <v>-2.9411764705882355</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="97">
         <v>6</v>
       </c>
@@ -18680,7 +18781,7 @@
         <f t="shared" si="2"/>
         <v>225</v>
       </c>
-      <c r="G7" s="151">
+      <c r="G7" s="150">
         <f t="shared" si="3"/>
         <v>4.7619047619047616E-2</v>
       </c>
@@ -18705,7 +18806,7 @@
         <v>-4.2857142857142856</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A8" s="97">
         <v>7</v>
       </c>
@@ -18727,7 +18828,7 @@
         <f t="shared" si="2"/>
         <v>36</v>
       </c>
-      <c r="G8" s="151">
+      <c r="G8" s="150">
         <f t="shared" si="3"/>
         <v>1.9607843137254902E-2</v>
       </c>
@@ -18752,7 +18853,7 @@
         <v>-5.2181818181818178</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="97">
         <v>8</v>
       </c>
@@ -18774,7 +18875,7 @@
         <f t="shared" si="2"/>
         <v>196</v>
       </c>
-      <c r="G9" s="151">
+      <c r="G9" s="150">
         <f t="shared" si="3"/>
         <v>4.8951048951048952E-2</v>
       </c>
@@ -18799,7 +18900,7 @@
         <v>-3.1304347826086953</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="97">
         <v>9</v>
       </c>
@@ -18821,7 +18922,7 @@
         <f t="shared" si="2"/>
         <v>64</v>
       </c>
-      <c r="G10" s="151">
+      <c r="G10" s="150">
         <f t="shared" si="3"/>
         <v>2.7397260273972601E-2</v>
       </c>
@@ -18846,7 +18947,7 @@
         <v>-2.2207792207792205</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="97">
         <v>10</v>
       </c>
@@ -18868,7 +18969,7 @@
         <f t="shared" si="2"/>
         <v>225</v>
       </c>
-      <c r="G11" s="151">
+      <c r="G11" s="150">
         <f t="shared" si="3"/>
         <v>5.2631578947368418E-2</v>
       </c>
@@ -18893,7 +18994,7 @@
         <v>-0.43478260869565188</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A12" s="97">
         <v>11</v>
       </c>
@@ -18915,7 +19016,7 @@
         <f t="shared" si="2"/>
         <v>121</v>
       </c>
-      <c r="G12" s="151">
+      <c r="G12" s="150">
         <f t="shared" si="3"/>
         <v>3.5369774919614148E-2</v>
       </c>
@@ -18940,7 +19041,7 @@
         <v>-1.6019417475728148</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A13" s="97">
         <v>12</v>
       </c>
@@ -18962,7 +19063,7 @@
         <f t="shared" si="2"/>
         <v>225</v>
       </c>
-      <c r="G13" s="151">
+      <c r="G13" s="150">
         <f t="shared" si="3"/>
         <v>5.2631578947368418E-2</v>
       </c>
@@ -18995,14 +19096,14 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EEA0E58-E4FC-F949-B5BB-1EF6C15622F5}">
   <dimension ref="A1:AA37"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.86328125" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="21" width="10.85546875" style="92"/>
-    <col min="22" max="27" width="10.85546875" style="100"/>
-    <col min="28" max="16384" width="10.85546875" style="92"/>
+    <col min="1" max="21" width="10.86328125" style="92"/>
+    <col min="22" max="27" width="10.86328125" style="100"/>
+    <col min="28" max="16384" width="10.86328125" style="92"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" ht="35.1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="106" t="s">
         <v>112</v>
       </c>
@@ -19043,7 +19144,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A2" s="97" t="s">
         <v>123</v>
       </c>
@@ -19085,7 +19186,7 @@
         <v>70.949999999999875</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A3" s="97" t="s">
         <v>123</v>
       </c>
@@ -19129,7 +19230,7 @@
         <v>70.949999999999875</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A4" s="97" t="s">
         <v>123</v>
       </c>
@@ -19173,7 +19274,7 @@
         <v>70.949999999999875</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A5" s="97" t="s">
         <v>123</v>
       </c>
@@ -19209,7 +19310,7 @@
         <v>70.949999999999875</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A6" s="97" t="s">
         <v>123</v>
       </c>
@@ -19245,7 +19346,7 @@
         <v>70.949999999999875</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A7" s="97" t="s">
         <v>123</v>
       </c>
@@ -19281,7 +19382,7 @@
         <v>70.949999999999875</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A8" s="97" t="s">
         <v>123</v>
       </c>
@@ -19317,7 +19418,7 @@
         <v>70.949999999999875</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A9" s="97" t="s">
         <v>123</v>
       </c>
@@ -19353,7 +19454,7 @@
         <v>70.949999999999875</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A10" s="97" t="s">
         <v>123</v>
       </c>
@@ -19389,7 +19490,7 @@
         <v>70.949999999999875</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A11" s="97" t="s">
         <v>123</v>
       </c>
@@ -19425,7 +19526,7 @@
         <v>70.949999999999875</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A12" s="97" t="s">
         <v>123</v>
       </c>
@@ -19461,7 +19562,7 @@
         <v>70.949999999999875</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A13" s="97" t="s">
         <v>123</v>
       </c>
@@ -19497,7 +19598,7 @@
         <v>70.949999999999875</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A14" s="93"/>
       <c r="B14" s="93"/>
       <c r="C14" s="93"/>
@@ -19517,7 +19618,7 @@
         <v>70.949999999999875</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A15" s="93"/>
       <c r="B15" s="93"/>
       <c r="C15" s="93"/>
@@ -19537,7 +19638,7 @@
         <v>70.949999999999875</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A16" s="93"/>
       <c r="B16" s="93"/>
       <c r="C16" s="93"/>
@@ -19557,7 +19658,7 @@
         <v>70.949999999999875</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A17" s="93"/>
       <c r="B17" s="93"/>
       <c r="C17" s="93"/>
@@ -19577,7 +19678,7 @@
         <v>70.949999999999875</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A18" s="93"/>
       <c r="B18" s="93"/>
       <c r="C18" s="93"/>
@@ -19597,7 +19698,7 @@
         <v>70.949999999999875</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A19" s="93"/>
       <c r="B19" s="93"/>
       <c r="C19" s="93"/>
@@ -19617,7 +19718,7 @@
         <v>70.949999999999875</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A20" s="93"/>
       <c r="B20" s="93"/>
       <c r="C20" s="93"/>
@@ -19637,7 +19738,7 @@
         <v>70.949999999999875</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A21" s="93"/>
       <c r="B21" s="93"/>
       <c r="C21" s="93"/>
@@ -19657,7 +19758,7 @@
         <v>70.949999999999875</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A22" s="93"/>
       <c r="B22" s="93"/>
       <c r="C22" s="93"/>
@@ -19677,7 +19778,7 @@
         <v>70.949999999999875</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A23" s="93"/>
       <c r="B23" s="93"/>
       <c r="C23" s="93"/>
@@ -19697,7 +19798,7 @@
         <v>70.949999999999875</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A24" s="93"/>
       <c r="B24" s="93"/>
       <c r="C24" s="93"/>
@@ -19717,7 +19818,7 @@
         <v>70.949999999999875</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A25" s="93"/>
       <c r="B25" s="93"/>
       <c r="C25" s="93"/>
@@ -19737,7 +19838,7 @@
         <v>70.949999999999875</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A26" s="93"/>
       <c r="B26" s="93"/>
       <c r="C26" s="93"/>
@@ -19757,7 +19858,7 @@
         <v>70.949999999999875</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A27" s="93"/>
       <c r="B27" s="93"/>
       <c r="C27" s="93"/>
@@ -19777,7 +19878,7 @@
         <v>70.949999999999875</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A28" s="93"/>
       <c r="B28" s="93"/>
       <c r="C28" s="93"/>
@@ -19797,7 +19898,7 @@
         <v>70.949999999999875</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A29" s="93"/>
       <c r="B29" s="93"/>
       <c r="C29" s="93"/>
@@ -19817,7 +19918,7 @@
         <v>70.949999999999875</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A30" s="93"/>
       <c r="B30" s="93"/>
       <c r="C30" s="93"/>
@@ -19837,7 +19938,7 @@
         <v>70.949999999999875</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A31" s="93"/>
       <c r="B31" s="93"/>
       <c r="C31" s="93"/>
@@ -19857,7 +19958,7 @@
         <v>70.949999999999875</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A32" s="93"/>
       <c r="B32" s="93"/>
       <c r="C32" s="93"/>
@@ -19877,7 +19978,7 @@
         <v>70.949999999999875</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A33" s="93"/>
       <c r="B33" s="93"/>
       <c r="C33" s="93"/>
@@ -19897,7 +19998,7 @@
         <v>70.949999999999875</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A34" s="93"/>
       <c r="B34" s="93"/>
       <c r="C34" s="93"/>
@@ -19917,7 +20018,7 @@
         <v>70.949999999999875</v>
       </c>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A35" s="93"/>
       <c r="B35" s="93"/>
       <c r="C35" s="93"/>
@@ -19937,7 +20038,7 @@
         <v>70.949999999999875</v>
       </c>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A36" s="93"/>
       <c r="B36" s="93"/>
       <c r="C36" s="93"/>
@@ -19957,7 +20058,7 @@
         <v>70.949999999999875</v>
       </c>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A37" s="93"/>
       <c r="B37" s="93"/>
       <c r="C37" s="93"/>
@@ -19986,13 +20087,13 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="6" max="6" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="13.86328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.1328125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
@@ -20021,7 +20122,7 @@
         <v>0.29808133083174404</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" s="17">
         <v>1</v>
       </c>
@@ -20046,7 +20147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" s="17">
         <v>2</v>
       </c>
@@ -20081,7 +20182,7 @@
         <v>5.7983454731007944</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" s="17">
         <v>3</v>
       </c>
@@ -20108,15 +20209,15 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I4" s="162" t="s">
+      <c r="I4" s="161" t="s">
         <v>109</v>
       </c>
-      <c r="J4" s="149">
+      <c r="J4" s="148">
         <f>AVERAGE(F3:F11)</f>
         <v>4.3146464464225351</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" s="17">
         <v>4</v>
       </c>
@@ -20144,7 +20245,7 @@
         <v>23.113735796723134</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" s="17">
         <v>5</v>
       </c>
@@ -20172,7 +20273,7 @@
         <v>2.7378471527578427</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" s="17">
         <v>6</v>
       </c>
@@ -20200,7 +20301,7 @@
         <v>161.22518072142719</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" s="17">
         <v>7</v>
       </c>
@@ -20228,7 +20329,7 @@
         <v>18.803274529379678</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" s="17">
         <v>8</v>
       </c>
@@ -20256,7 +20357,7 @@
         <v>3.7081610853418757E-13</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" s="17">
         <v>9</v>
       </c>
@@ -20284,7 +20385,7 @@
         <v>64.70131429570003</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" s="17">
         <v>10</v>
       </c>
@@ -20312,7 +20413,7 @@
         <v>28.005939532867973</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" s="15">
         <v>11</v>
       </c>
@@ -20325,14 +20426,14 @@
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C13" s="1"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C14" s="1"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -20348,14 +20449,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.140625" customWidth="1"/>
-    <col min="2" max="2" width="9.42578125" customWidth="1"/>
-    <col min="3" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1328125" customWidth="1"/>
+    <col min="2" max="2" width="9.3984375" customWidth="1"/>
+    <col min="3" max="5" width="11.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
@@ -20375,7 +20476,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="15">
         <v>1</v>
       </c>
@@ -20386,7 +20487,7 @@
       <c r="D2" s="53"/>
       <c r="E2" s="112"/>
     </row>
-    <row r="3" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="15">
         <v>2</v>
       </c>
@@ -20397,7 +20498,7 @@
       <c r="D3" s="53"/>
       <c r="E3" s="112"/>
     </row>
-    <row r="4" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="15">
         <v>3</v>
       </c>
@@ -20411,7 +20512,7 @@
       </c>
       <c r="E4" s="112"/>
     </row>
-    <row r="5" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="15">
         <v>4</v>
       </c>
@@ -20429,7 +20530,7 @@
       <c r="E5" s="112"/>
       <c r="G5" s="72"/>
     </row>
-    <row r="6" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="15">
         <v>5</v>
       </c>
@@ -20446,7 +20547,7 @@
       </c>
       <c r="E6" s="112"/>
     </row>
-    <row r="7" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="15">
         <v>6</v>
       </c>
@@ -20466,7 +20567,7 @@
         <v>85.2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="15">
         <v>7</v>
       </c>
@@ -20486,7 +20587,7 @@
         <v>106.8</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="15">
         <v>8</v>
       </c>
@@ -20506,7 +20607,7 @@
         <v>130.6</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="15">
         <v>9</v>
       </c>
@@ -20526,7 +20627,7 @@
         <v>153.19999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="15">
         <v>10</v>
       </c>
@@ -20546,7 +20647,7 @@
         <v>173.2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="15">
         <v>11</v>
       </c>
@@ -20564,7 +20665,7 @@
         <v>193.2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="15">
         <v>12</v>
       </c>
@@ -20582,7 +20683,7 @@
         <v>193.2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="15">
         <v>13</v>
       </c>
@@ -20609,14 +20710,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5485D312-2BE2-9B4D-9886-4523BCC91604}">
   <dimension ref="A1:H16"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.140625" customWidth="1"/>
-    <col min="2" max="2" width="9.42578125" customWidth="1"/>
-    <col min="3" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1328125" customWidth="1"/>
+    <col min="2" max="2" width="9.3984375" customWidth="1"/>
+    <col min="3" max="5" width="11.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
@@ -20642,7 +20743,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="15">
         <v>1</v>
       </c>
@@ -20656,7 +20757,7 @@
       <c r="G2" s="112"/>
       <c r="H2" s="112"/>
     </row>
-    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="15">
         <v>2</v>
       </c>
@@ -20670,7 +20771,7 @@
       <c r="G3" s="112"/>
       <c r="H3" s="112"/>
     </row>
-    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="15">
         <v>3</v>
       </c>
@@ -20690,7 +20791,7 @@
       </c>
       <c r="H4" s="112"/>
     </row>
-    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="15">
         <v>4</v>
       </c>
@@ -20716,7 +20817,7 @@
       </c>
       <c r="H5" s="112"/>
     </row>
-    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="15">
         <v>5</v>
       </c>
@@ -20742,7 +20843,7 @@
       </c>
       <c r="H6" s="112"/>
     </row>
-    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="15">
         <v>6</v>
       </c>
@@ -20774,7 +20875,7 @@
         <v>3.5999999999999943</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="15">
         <v>7</v>
       </c>
@@ -20806,7 +20907,7 @@
         <v>4.4000000000000057</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="15">
         <v>8</v>
       </c>
@@ -20838,7 +20939,7 @@
         <v>0.59999999999999432</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="15">
         <v>9</v>
       </c>
@@ -20870,7 +20971,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="15">
         <v>10</v>
       </c>
@@ -20902,7 +21003,7 @@
         <v>3.1999999999999886</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="15">
         <v>11</v>
       </c>
@@ -20923,7 +21024,7 @@
       <c r="G12" s="112"/>
       <c r="H12" s="112"/>
     </row>
-    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="15">
         <v>12</v>
       </c>
@@ -20944,7 +21045,7 @@
       <c r="G13" s="53"/>
       <c r="H13" s="53"/>
     </row>
-    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="15">
         <v>13</v>
       </c>
@@ -20965,7 +21066,7 @@
       <c r="G14" s="53"/>
       <c r="H14" s="53"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="F15" s="115">
         <f>AVERAGE(F4:F14)</f>
         <v>3.047619047619047</v>
@@ -20979,12 +21080,12 @@
         <v>3.5599999999999965</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F16" s="175" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="F16" s="174" t="s">
         <v>8</v>
       </c>
-      <c r="G16" s="175"/>
-      <c r="H16" s="175"/>
+      <c r="G16" s="174"/>
+      <c r="H16" s="174"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -20997,30 +21098,30 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C0BBF5C-6828-434A-8CCD-CE2E5A08C4DE}">
-  <dimension ref="B2:L19"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:L23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="12" width="18.28515625" customWidth="1"/>
+    <col min="2" max="12" width="18.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B2" s="10"/>
-      <c r="C2" s="176" t="s">
+      <c r="C2" s="175" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="177"/>
-      <c r="E2" s="177"/>
-      <c r="F2" s="177"/>
-      <c r="G2" s="178"/>
-      <c r="H2" s="176" t="s">
+      <c r="D2" s="176"/>
+      <c r="E2" s="176"/>
+      <c r="F2" s="176"/>
+      <c r="G2" s="177"/>
+      <c r="H2" s="175" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="177"/>
-      <c r="J2" s="177"/>
-      <c r="K2" s="177"/>
-      <c r="L2" s="178"/>
-    </row>
-    <row r="3" spans="2:12" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I2" s="176"/>
+      <c r="J2" s="176"/>
+      <c r="K2" s="176"/>
+      <c r="L2" s="177"/>
+    </row>
+    <row r="3" spans="2:12" ht="25.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B3" s="11" t="s">
         <v>11</v>
       </c>
@@ -21055,7 +21156,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="2:12" ht="27" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="25.9" thickTop="1" x14ac:dyDescent="0.45">
       <c r="B4" s="9" t="s">
         <v>21</v>
       </c>
@@ -21090,7 +21191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B5" s="10" t="s">
         <v>22</v>
       </c>
@@ -21121,7 +21222,7 @@
       </c>
       <c r="L5" s="10"/>
     </row>
-    <row r="6" spans="2:12" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B6" s="10" t="s">
         <v>23</v>
       </c>
@@ -21150,7 +21251,7 @@
       </c>
       <c r="L6" s="10"/>
     </row>
-    <row r="7" spans="2:12" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B7" s="10" t="s">
         <v>24</v>
       </c>
@@ -21177,7 +21278,7 @@
       </c>
       <c r="L7" s="10"/>
     </row>
-    <row r="8" spans="2:12" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B8" s="10" t="s">
         <v>25</v>
       </c>
@@ -21200,8 +21301,10 @@
       <c r="K8" s="8"/>
       <c r="L8" s="10"/>
     </row>
-    <row r="13" spans="2:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="H13" s="8">
+    <row r="13" spans="2:12" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="F13" s="178"/>
+      <c r="G13" s="178"/>
+      <c r="H13" s="179">
         <v>0.2</v>
       </c>
       <c r="I13" s="8">
@@ -21217,11 +21320,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="G14" s="145">
+    <row r="14" spans="2:12" ht="25.5" x14ac:dyDescent="0.75">
+      <c r="F14" s="178"/>
+      <c r="G14" s="178">
         <v>0</v>
       </c>
-      <c r="H14" s="143">
+      <c r="H14" s="180">
         <f>((1-H$13)^$G14)*H$13</f>
         <v>0.2</v>
       </c>
@@ -21241,16 +21345,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="2:12" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="G15" s="145">
+    <row r="15" spans="2:12" ht="25.5" x14ac:dyDescent="0.75">
+      <c r="F15" s="178"/>
+      <c r="G15" s="178">
         <v>1</v>
       </c>
-      <c r="H15" s="143">
+      <c r="H15" s="180">
         <f t="shared" ref="H15:L18" si="1">((1-H$13)^$G15)*H$13</f>
         <v>0.16000000000000003</v>
       </c>
       <c r="I15" s="144">
-        <f t="shared" si="1"/>
+        <f>((1-I$13)^$G15)*I$13</f>
         <v>0.24</v>
       </c>
       <c r="J15" s="144">
@@ -21266,11 +21371,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="G16" s="145">
+    <row r="16" spans="2:12" ht="25.5" x14ac:dyDescent="0.75">
+      <c r="F16" s="178"/>
+      <c r="G16" s="178">
         <v>2</v>
       </c>
-      <c r="H16" s="143">
+      <c r="H16" s="180">
         <f t="shared" si="1"/>
         <v>0.12800000000000003</v>
       </c>
@@ -21291,11 +21397,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="G17" s="145">
+    <row r="17" spans="6:12" ht="25.5" x14ac:dyDescent="0.75">
+      <c r="F17" s="178"/>
+      <c r="G17" s="178">
         <v>3</v>
       </c>
-      <c r="H17" s="143">
+      <c r="H17" s="180">
         <f t="shared" si="1"/>
         <v>0.10240000000000003</v>
       </c>
@@ -21316,11 +21423,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="G18" s="145">
+    <row r="18" spans="6:12" ht="25.5" x14ac:dyDescent="0.75">
+      <c r="F18" s="178"/>
+      <c r="G18" s="178">
         <v>4</v>
       </c>
-      <c r="H18" s="143">
+      <c r="H18" s="180">
         <f>((1-H$13)^$G18)*H$13</f>
         <v>8.1920000000000048E-2</v>
       </c>
@@ -21341,15 +21449,36 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="G19" s="145">
+    <row r="19" spans="6:12" ht="25.5" x14ac:dyDescent="0.75">
+      <c r="F19" s="178"/>
+      <c r="G19" s="178">
         <v>5</v>
       </c>
-      <c r="H19" s="143"/>
+      <c r="H19" s="180"/>
       <c r="I19" s="143"/>
       <c r="J19" s="143"/>
       <c r="K19" s="143"/>
       <c r="L19" s="143"/>
+    </row>
+    <row r="20" spans="6:12" x14ac:dyDescent="0.45">
+      <c r="F20" s="178"/>
+      <c r="G20" s="178"/>
+      <c r="H20" s="178"/>
+    </row>
+    <row r="21" spans="6:12" x14ac:dyDescent="0.45">
+      <c r="F21" s="178"/>
+      <c r="G21" s="178"/>
+      <c r="H21" s="178"/>
+    </row>
+    <row r="22" spans="6:12" x14ac:dyDescent="0.45">
+      <c r="F22" s="178"/>
+      <c r="G22" s="178"/>
+      <c r="H22" s="178"/>
+    </row>
+    <row r="23" spans="6:12" x14ac:dyDescent="0.45">
+      <c r="F23" s="178"/>
+      <c r="G23" s="178"/>
+      <c r="H23" s="178"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -21364,12 +21493,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="3" width="9.42578125" customWidth="1"/>
+    <col min="1" max="3" width="9.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
@@ -21386,7 +21515,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="15">
         <v>1</v>
       </c>
@@ -21397,7 +21526,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="15">
         <v>2</v>
       </c>
@@ -21409,7 +21538,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="15">
         <v>3</v>
       </c>
@@ -21421,7 +21550,7 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="15">
         <v>4</v>
       </c>
@@ -21433,7 +21562,7 @@
         <v>50.28</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="15">
         <v>5</v>
       </c>
@@ -21445,7 +21574,7 @@
         <v>62.624000000000009</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="15">
         <v>6</v>
       </c>
@@ -21457,7 +21586,7 @@
         <v>76.499200000000016</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="15">
         <v>7</v>
       </c>
@@ -21469,7 +21598,7 @@
         <v>90.199360000000013</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" s="15">
         <v>8</v>
       </c>
@@ -21481,7 +21610,7 @@
         <v>107.95948800000002</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" s="15">
         <v>9</v>
       </c>
@@ -21493,7 +21622,7 @@
         <v>125.96759040000003</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" s="15">
         <v>10</v>
       </c>
@@ -21505,7 +21634,7 @@
         <v>143.17407232000005</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="15">
         <v>11</v>
       </c>
@@ -21515,7 +21644,7 @@
         <v>160.93925785600004</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" s="15">
         <v>12</v>
       </c>
@@ -21525,7 +21654,7 @@
         <v>160.93925785600004</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" s="15">
         <v>13</v>
       </c>
@@ -21544,14 +21673,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
@@ -21574,7 +21703,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="53">
         <v>1</v>
       </c>
@@ -21597,7 +21726,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" s="53">
         <v>2</v>
       </c>
@@ -21617,7 +21746,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" s="53">
         <v>3</v>
       </c>
@@ -21637,7 +21766,7 @@
         <v>23.239999999999995</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" s="53">
         <v>4</v>
       </c>
@@ -21657,7 +21786,7 @@
         <v>23.859199999999991</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" s="53">
         <v>5</v>
       </c>
@@ -21677,7 +21806,7 @@
         <v>23.829535999999987</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" s="53">
         <v>6</v>
       </c>
@@ -21697,7 +21826,7 @@
         <v>22.50922688</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" s="53">
         <v>7</v>
       </c>
@@ -21717,7 +21846,7 @@
         <v>22.963903270399992</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" s="53">
         <v>8</v>
       </c>
@@ -21737,7 +21866,7 @@
         <v>22.80650835123199</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="53">
         <v>9</v>
       </c>
@@ -21757,7 +21886,7 @@
         <v>21.639550905666557</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" s="53">
         <v>10</v>
       </c>
@@ -21777,7 +21906,7 @@
         <v>20.625934585090768</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" s="53">
         <v>11</v>
       </c>
@@ -21789,7 +21918,7 @@
       <c r="D12" s="53"/>
       <c r="E12" s="53"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" s="53">
         <v>12</v>
       </c>
@@ -21801,7 +21930,7 @@
       <c r="D13" s="53"/>
       <c r="E13" s="53"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" s="53">
         <v>13</v>
       </c>
@@ -21822,12 +21951,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:K19"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="9" max="11" width="8.85546875" customWidth="1"/>
+    <col min="9" max="11" width="8.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
@@ -21850,19 +21979,19 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" s="73">
         <v>1</v>
       </c>
       <c r="B2" s="73">
         <v>37</v>
       </c>
-      <c r="C2" s="146"/>
-      <c r="D2" s="147">
+      <c r="C2" s="145"/>
+      <c r="D2" s="146">
         <f>B2</f>
         <v>37</v>
       </c>
-      <c r="E2" s="147">
+      <c r="E2" s="146">
         <f>B3-B2</f>
         <v>33</v>
       </c>
@@ -21881,7 +22010,7 @@
         <v>5.7157760961359019</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" s="73">
         <v>2</v>
       </c>
@@ -21911,7 +22040,7 @@
         <v>6.5999999999999943</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" s="73">
         <v>3</v>
       </c>
@@ -21935,7 +22064,7 @@
         <v>12.866399999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" s="73">
         <v>4</v>
       </c>
@@ -21959,7 +22088,7 @@
         <v>15.368425600000009</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" s="73">
         <v>5</v>
       </c>
@@ -21983,7 +22112,7 @@
         <v>6.3720855424000149</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" s="73">
         <v>6</v>
       </c>
@@ -22007,7 +22136,7 @@
         <v>3.7400897655296035</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" s="73">
         <v>7</v>
       </c>
@@ -22031,7 +22160,7 @@
         <v>1.2827181270595531</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" s="73">
         <v>8</v>
       </c>
@@ -22055,7 +22184,7 @@
         <v>0.29351401830493273</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10" s="73">
         <v>9</v>
       </c>
@@ -22074,7 +22203,7 @@
         <f t="shared" si="3"/>
         <v>7.0213061200976199</v>
       </c>
-      <c r="G10" s="152">
+      <c r="G10" s="151">
         <v>37</v>
       </c>
       <c r="H10">
@@ -22085,7 +22214,7 @@
         <v>2.5304158328534925</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11" s="73">
         <v>10</v>
       </c>
@@ -22104,7 +22233,7 @@
         <f>$H$2*(D11-D10)+(1-$H$2)*E10*$H$3</f>
         <v>5.330444578589022</v>
       </c>
-      <c r="G11" s="152">
+      <c r="G11" s="151">
         <v>70</v>
       </c>
       <c r="H11">
@@ -22115,7 +22244,7 @@
         <v>2.3883359790755208</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A12" s="73">
         <v>11</v>
       </c>
@@ -22126,14 +22255,14 @@
       </c>
       <c r="D12" s="73"/>
       <c r="E12" s="73"/>
-      <c r="G12" s="152">
+      <c r="G12" s="151">
         <v>100</v>
       </c>
       <c r="H12">
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A13" s="73">
         <v>12</v>
       </c>
@@ -22144,14 +22273,14 @@
       </c>
       <c r="D13" s="73"/>
       <c r="E13" s="73"/>
-      <c r="G13" s="152">
+      <c r="G13" s="151">
         <v>125</v>
       </c>
       <c r="H13">
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A14" s="73">
         <v>13</v>
       </c>
@@ -22162,47 +22291,47 @@
       </c>
       <c r="D14" s="73"/>
       <c r="E14" s="73"/>
-      <c r="G14" s="152">
+      <c r="G14" s="151">
         <v>137</v>
       </c>
       <c r="H14">
         <v>132</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="G15" s="152">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="G15" s="151">
         <v>150</v>
       </c>
       <c r="H15">
         <v>145</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="G16" s="152">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="G16" s="151">
         <v>160</v>
       </c>
       <c r="H16">
         <v>179</v>
       </c>
     </row>
-    <row r="17" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G17" s="152">
+    <row r="17" spans="7:8" x14ac:dyDescent="0.45">
+      <c r="G17" s="151">
         <v>168</v>
       </c>
       <c r="H17">
         <v>198</v>
       </c>
     </row>
-    <row r="18" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G18" s="152">
+    <row r="18" spans="7:8" x14ac:dyDescent="0.45">
+      <c r="G18" s="151">
         <v>173</v>
       </c>
       <c r="H18">
         <v>212</v>
       </c>
     </row>
-    <row r="19" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G19" s="152">
+    <row r="19" spans="7:8" x14ac:dyDescent="0.45">
+      <c r="G19" s="151">
         <v>178</v>
       </c>
       <c r="H19">
@@ -22218,19 +22347,19 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.265625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.42578125" style="5" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" style="1"/>
+    <col min="7" max="7" width="9.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.3984375" style="5" customWidth="1"/>
+    <col min="9" max="9" width="9.1328125" style="1"/>
     <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="72" t="s">
         <v>31</v>
       </c>
@@ -22263,7 +22392,7 @@
       </c>
       <c r="M1" s="6"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A2" s="72">
         <v>1</v>
       </c>
@@ -22297,7 +22426,7 @@
       </c>
       <c r="M2" s="7"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3" s="72">
         <v>1</v>
       </c>
@@ -22310,12 +22439,12 @@
       <c r="D3" s="15">
         <v>10</v>
       </c>
-      <c r="E3" s="155"/>
-      <c r="F3" s="153">
+      <c r="E3" s="154"/>
+      <c r="F3" s="152">
         <f>$K$1*D3/H3+(1-$K$1)*(F2+G2)</f>
         <v>8.6702127659574462</v>
       </c>
-      <c r="G3" s="153">
+      <c r="G3" s="152">
         <f>$K$2*(F3-F2)+(1-$K$2)*G2</f>
         <v>1.7967187900538324</v>
       </c>
@@ -22331,7 +22460,7 @@
       </c>
       <c r="M3" s="7"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A4" s="72">
         <v>1</v>
       </c>
@@ -22344,12 +22473,12 @@
       <c r="D4" s="15">
         <v>6</v>
       </c>
-      <c r="E4" s="155"/>
-      <c r="F4" s="153">
+      <c r="E4" s="154"/>
+      <c r="F4" s="152">
         <f>$K$1*D4/H4+(1-$K$1)*(F3+G3)</f>
         <v>10.243386311202258</v>
       </c>
-      <c r="G4" s="153">
+      <c r="G4" s="152">
         <f>$K$2*(F4-F3)+(1-$K$2)*G3</f>
         <v>1.7743642655729304</v>
       </c>
@@ -22359,7 +22488,7 @@
       </c>
       <c r="M4" s="7"/>
     </row>
-    <row r="5" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="72">
         <v>1</v>
       </c>
@@ -22372,12 +22501,12 @@
       <c r="D5" s="131">
         <v>2</v>
       </c>
-      <c r="E5" s="156"/>
-      <c r="F5" s="154">
+      <c r="E5" s="155"/>
+      <c r="F5" s="153">
         <f>$K$1*D5/H5+(1-$K$1)*(F4+G4)</f>
         <v>9.6479945597994821</v>
       </c>
-      <c r="G5" s="154">
+      <c r="G5" s="153">
         <f t="shared" ref="G5:G20" si="0">$K$2*(F5-F4)+(1-$K$2)*G4</f>
         <v>1.5373886638753598</v>
       </c>
@@ -22386,7 +22515,7 @@
         <v>0.22085889570552147</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A6" s="72">
         <v>2</v>
       </c>
@@ -22416,7 +22545,7 @@
         <v>1.9957007937400659</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A7" s="72">
         <v>2</v>
       </c>
@@ -22446,7 +22575,7 @@
         <v>1.1086783708753742</v>
       </c>
     </row>
-    <row r="8" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A8" s="72">
         <v>2</v>
       </c>
@@ -22480,7 +22609,7 @@
       <c r="L8"/>
       <c r="M8"/>
     </row>
-    <row r="9" spans="1:13" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" s="1" customFormat="1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A9" s="72">
         <v>2</v>
       </c>
@@ -22514,7 +22643,7 @@
       <c r="L9"/>
       <c r="M9"/>
     </row>
-    <row r="10" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A10" s="72">
         <v>3</v>
       </c>
@@ -22548,7 +22677,7 @@
       <c r="L10"/>
       <c r="M10"/>
     </row>
-    <row r="11" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A11" s="72">
         <v>3</v>
       </c>
@@ -22582,7 +22711,7 @@
       <c r="L11"/>
       <c r="M11"/>
     </row>
-    <row r="12" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A12" s="72">
         <v>3</v>
       </c>
@@ -22616,7 +22745,7 @@
       <c r="L12"/>
       <c r="M12"/>
     </row>
-    <row r="13" spans="1:13" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" s="1" customFormat="1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A13" s="72">
         <v>3</v>
       </c>
@@ -22650,7 +22779,7 @@
       <c r="L13"/>
       <c r="M13"/>
     </row>
-    <row r="14" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A14" s="72">
         <v>4</v>
       </c>
@@ -22684,7 +22813,7 @@
       <c r="L14"/>
       <c r="M14"/>
     </row>
-    <row r="15" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A15" s="72">
         <v>4</v>
       </c>
@@ -22718,7 +22847,7 @@
       <c r="L15"/>
       <c r="M15"/>
     </row>
-    <row r="16" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A16" s="72">
         <v>4</v>
       </c>
@@ -22752,7 +22881,7 @@
       <c r="L16"/>
       <c r="M16"/>
     </row>
-    <row r="17" spans="1:13" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" s="1" customFormat="1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A17" s="72">
         <v>4</v>
       </c>
@@ -22786,7 +22915,7 @@
       <c r="L17"/>
       <c r="M17"/>
     </row>
-    <row r="18" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A18" s="72">
         <v>5</v>
       </c>
@@ -22820,7 +22949,7 @@
       <c r="L18"/>
       <c r="M18"/>
     </row>
-    <row r="19" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A19" s="72">
         <v>5</v>
       </c>
@@ -22854,7 +22983,7 @@
       <c r="L19"/>
       <c r="M19"/>
     </row>
-    <row r="20" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A20" s="72">
         <v>5</v>
       </c>
@@ -22888,7 +23017,7 @@
       <c r="L20"/>
       <c r="M20"/>
     </row>
-    <row r="21" spans="1:13" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" s="1" customFormat="1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A21" s="72">
         <v>5</v>
       </c>
@@ -22922,7 +23051,7 @@
       <c r="L21"/>
       <c r="M21"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A22" s="72">
         <v>6</v>
       </c>
@@ -22941,7 +23070,7 @@
       <c r="G22" s="140"/>
       <c r="H22" s="141"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A23" s="72">
         <v>6</v>
       </c>
@@ -22960,7 +23089,7 @@
       <c r="G23" s="118"/>
       <c r="H23" s="119"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A24" s="72">
         <v>6</v>
       </c>
@@ -22979,7 +23108,7 @@
       <c r="G24" s="118"/>
       <c r="H24" s="119"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A25" s="72">
         <v>6</v>
       </c>
@@ -23007,19 +23136,19 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:K25"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.265625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.42578125" style="5" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="1"/>
+    <col min="5" max="5" width="9.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.3984375" style="5" customWidth="1"/>
+    <col min="7" max="7" width="9.1328125" style="1"/>
     <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -23049,23 +23178,23 @@
       </c>
       <c r="K1" s="6"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" s="73">
         <v>1</v>
       </c>
-      <c r="B2" s="148">
+      <c r="B2" s="147">
         <v>14</v>
       </c>
-      <c r="C2" s="150"/>
-      <c r="D2" s="149">
+      <c r="C2" s="149"/>
+      <c r="D2" s="148">
         <f>B2-F2</f>
         <v>5.5</v>
       </c>
-      <c r="E2" s="149">
+      <c r="E2" s="148">
         <f>(B3-F3)-(B2-F2)</f>
         <v>3.1999999999999993</v>
       </c>
-      <c r="F2" s="149">
+      <c r="F2" s="148">
         <f>ROUND(AVERAGE(B2,B6,B10,B14,B18)-AVERAGE($B$2:$B$21),1)</f>
         <v>8.5</v>
       </c>
@@ -23077,11 +23206,11 @@
       </c>
       <c r="K2" s="7"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" s="73">
         <v>2</v>
       </c>
-      <c r="B3" s="148">
+      <c r="B3" s="147">
         <v>10</v>
       </c>
       <c r="C3" s="53">
@@ -23096,7 +23225,7 @@
         <f>$I$2*(D3-D2)+(1-$I$2)*E2</f>
         <v>3.1999999999999993</v>
       </c>
-      <c r="F3" s="149">
+      <c r="F3" s="148">
         <f>ROUND(AVERAGE(B3,B7,B11,B15,B19)-AVERAGE($B$2:$B$21),1)</f>
         <v>1.3</v>
       </c>
@@ -23108,11 +23237,11 @@
       </c>
       <c r="K3" s="7"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" s="73">
         <v>3</v>
       </c>
-      <c r="B4" s="148">
+      <c r="B4" s="147">
         <v>6</v>
       </c>
       <c r="C4" s="53">
@@ -23127,17 +23256,17 @@
         <f>$I$2*(D4-D3)+(1-$I$2)*E3</f>
         <v>2.9999999999999996</v>
       </c>
-      <c r="F4" s="149">
+      <c r="F4" s="148">
         <f t="shared" ref="F4:F5" si="1">ROUND(AVERAGE(B4,B8,B12,B16,B20)-AVERAGE($B$2:$B$21),1)</f>
         <v>-3.4</v>
       </c>
       <c r="K4" s="7"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" s="73">
         <v>4</v>
       </c>
-      <c r="B5" s="148">
+      <c r="B5" s="147">
         <v>2</v>
       </c>
       <c r="C5" s="53">
@@ -23152,16 +23281,16 @@
         <f>$I$2*(D5-D4)+(1-$I$2)*E4</f>
         <v>2.64</v>
       </c>
-      <c r="F5" s="149">
+      <c r="F5" s="148">
         <f t="shared" si="1"/>
         <v>-6.4</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" s="73">
         <v>5</v>
       </c>
-      <c r="B6" s="148">
+      <c r="B6" s="147">
         <v>18</v>
       </c>
       <c r="C6" s="53">
@@ -23181,11 +23310,11 @@
         <v>8.3048000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" s="73">
         <v>6</v>
       </c>
-      <c r="B7" s="148">
+      <c r="B7" s="147">
         <v>8</v>
       </c>
       <c r="C7" s="53">
@@ -23205,11 +23334,11 @@
         <v>0.8413759999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A8" s="73">
         <v>7</v>
       </c>
-      <c r="B8" s="148">
+      <c r="B8" s="147">
         <v>4</v>
       </c>
       <c r="C8" s="53">
@@ -23233,11 +23362,11 @@
       <c r="J8"/>
       <c r="K8"/>
     </row>
-    <row r="9" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A9" s="73">
         <v>8</v>
       </c>
-      <c r="B9" s="148">
+      <c r="B9" s="147">
         <v>1</v>
       </c>
       <c r="C9" s="53">
@@ -23261,11 +23390,11 @@
       <c r="J9"/>
       <c r="K9"/>
     </row>
-    <row r="10" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A10" s="73">
         <v>9</v>
       </c>
-      <c r="B10" s="148">
+      <c r="B10" s="147">
         <v>16</v>
       </c>
       <c r="C10" s="53">
@@ -23289,11 +23418,11 @@
       <c r="J10"/>
       <c r="K10"/>
     </row>
-    <row r="11" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A11" s="73">
         <v>10</v>
       </c>
-      <c r="B11" s="148">
+      <c r="B11" s="147">
         <v>9</v>
       </c>
       <c r="C11" s="53">
@@ -23317,11 +23446,11 @@
       <c r="J11"/>
       <c r="K11"/>
     </row>
-    <row r="12" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A12" s="73">
         <v>11</v>
       </c>
-      <c r="B12" s="148">
+      <c r="B12" s="147">
         <v>5</v>
       </c>
       <c r="C12" s="53">
@@ -23345,11 +23474,11 @@
       <c r="J12"/>
       <c r="K12"/>
     </row>
-    <row r="13" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A13" s="73">
         <v>12</v>
       </c>
-      <c r="B13" s="148">
+      <c r="B13" s="147">
         <v>3</v>
       </c>
       <c r="C13" s="53">
@@ -23373,11 +23502,11 @@
       <c r="J13"/>
       <c r="K13"/>
     </row>
-    <row r="14" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A14" s="73">
         <v>13</v>
       </c>
-      <c r="B14" s="148">
+      <c r="B14" s="147">
         <v>18</v>
       </c>
       <c r="C14" s="53">
@@ -23401,11 +23530,11 @@
       <c r="J14"/>
       <c r="K14"/>
     </row>
-    <row r="15" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A15" s="73">
         <v>14</v>
       </c>
-      <c r="B15" s="148">
+      <c r="B15" s="147">
         <v>11</v>
       </c>
       <c r="C15" s="53">
@@ -23429,11 +23558,11 @@
       <c r="J15"/>
       <c r="K15"/>
     </row>
-    <row r="16" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A16" s="73">
         <v>15</v>
       </c>
-      <c r="B16" s="148">
+      <c r="B16" s="147">
         <v>4</v>
       </c>
       <c r="C16" s="53">
@@ -23457,11 +23586,11 @@
       <c r="J16"/>
       <c r="K16"/>
     </row>
-    <row r="17" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A17" s="73">
         <v>16</v>
       </c>
-      <c r="B17" s="148">
+      <c r="B17" s="147">
         <v>2</v>
       </c>
       <c r="C17" s="53">
@@ -23485,11 +23614,11 @@
       <c r="J17"/>
       <c r="K17"/>
     </row>
-    <row r="18" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A18" s="73">
         <v>17</v>
       </c>
-      <c r="B18" s="148">
+      <c r="B18" s="147">
         <v>17</v>
       </c>
       <c r="C18" s="53">
@@ -23513,11 +23642,11 @@
       <c r="J18"/>
       <c r="K18"/>
     </row>
-    <row r="19" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A19" s="73">
         <v>18</v>
       </c>
-      <c r="B19" s="148">
+      <c r="B19" s="147">
         <v>9</v>
       </c>
       <c r="C19" s="53">
@@ -23541,11 +23670,11 @@
       <c r="J19"/>
       <c r="K19"/>
     </row>
-    <row r="20" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A20" s="73">
         <v>19</v>
       </c>
-      <c r="B20" s="148">
+      <c r="B20" s="147">
         <v>5</v>
       </c>
       <c r="C20" s="53">
@@ -23569,11 +23698,11 @@
       <c r="J20"/>
       <c r="K20"/>
     </row>
-    <row r="21" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A21" s="73">
         <v>20</v>
       </c>
-      <c r="B21" s="148">
+      <c r="B21" s="147">
         <v>1</v>
       </c>
       <c r="C21" s="53">
@@ -23597,7 +23726,7 @@
       <c r="J21"/>
       <c r="K21"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A22" s="73">
         <v>21</v>
       </c>
@@ -23618,7 +23747,7 @@
         <v>8.0352641228758035</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A23" s="73">
         <v>22</v>
       </c>
@@ -23639,7 +23768,7 @@
         <v>0.55069466093332575</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A24" s="73">
         <v>23</v>
       </c>
@@ -23660,7 +23789,7 @@
         <v>-4.0101363190712265</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A25" s="73">
         <v>24</v>
       </c>
@@ -23688,6 +23817,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A2D80723F61E8E48B44C32791AB79EAF" ma:contentTypeVersion="4" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="dfeb1cef9289b988e02c62b45d9f1082">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fb0af546-8adb-47f3-baac-5cb4c71f4200" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e941073ceb027b680dcaca81f0d1cb22" ns2:_="">
     <xsd:import namespace="fb0af546-8adb-47f3-baac-5cb4c71f4200"/>
@@ -23831,22 +23975,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1362C07F-B5AC-4985-9E08-9C1EEC3CADCF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1972A55-6FB5-450D-A0FF-51E9D87A8333}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35A6F954-B64F-43DA-86C7-62E62C188AF3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -23862,21 +24008,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1972A55-6FB5-450D-A0FF-51E9D87A8333}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1362C07F-B5AC-4985-9E08-9C1EEC3CADCF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>